--- a/data/latest/camera_statistics.xlsx
+++ b/data/latest/camera_statistics.xlsx
@@ -231,7 +231,7 @@
       <valAx>
         <axId val="100"/>
         <scaling>
-          <orientation val="maxMin"/>
+          <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
         <majorGridlines/>
